--- a/web/public/forms/minwon.xlsx
+++ b/web/public/forms/minwon.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="민원 접수·처리대장" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'민원 접수·처리대장'!$A$1:$X$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy. m. d."/>
+    <numFmt numFmtId="165" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,32 +37,48 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000F203F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="006B7280"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="00111827"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,12 +87,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FC"/>
+        <fgColor rgb="00F3F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3FB"/>
+        <fgColor rgb="00E8EEF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF4FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,23 +111,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,32 +136,50 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -530,15 +575,15 @@
     <col width="3.6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵   |   k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다   </t>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
         </is>
       </c>
     </row>
@@ -562,7 +607,7 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
@@ -592,7 +637,7 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
@@ -671,320 +716,356 @@
       <c r="X8" s="5" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="8" t="inlineStr"/>
+      <c r="A9" s="8">
+        <f>IF(K9="","",COUNTA(K9:K9))</f>
+        <v/>
+      </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="8" t="inlineStr"/>
+      <c r="C9" s="9" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="8" t="inlineStr"/>
+      <c r="E9" s="10" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="5" t="n"/>
-      <c r="H9" s="8" t="inlineStr"/>
+      <c r="H9" s="10" t="n"/>
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
-      <c r="K9" s="8" t="inlineStr"/>
+      <c r="K9" s="10" t="n"/>
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="5" t="n"/>
       <c r="N9" s="5" t="n"/>
       <c r="O9" s="5" t="n"/>
-      <c r="P9" s="8" t="inlineStr"/>
+      <c r="P9" s="10" t="n"/>
       <c r="Q9" s="5" t="n"/>
       <c r="R9" s="5" t="n"/>
       <c r="S9" s="5" t="n"/>
       <c r="T9" s="5" t="n"/>
-      <c r="U9" s="8" t="inlineStr"/>
+      <c r="U9" s="9" t="n"/>
       <c r="V9" s="5" t="n"/>
-      <c r="W9" s="8" t="inlineStr"/>
+      <c r="W9" s="10" t="n"/>
       <c r="X9" s="5" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr"/>
+      <c r="A10" s="8">
+        <f>IF(K10="","",COUNTA(K9:K10))</f>
+        <v/>
+      </c>
       <c r="B10" s="5" t="n"/>
-      <c r="C10" s="8" t="inlineStr"/>
+      <c r="C10" s="9" t="n"/>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="8" t="inlineStr"/>
+      <c r="E10" s="10" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n"/>
-      <c r="H10" s="8" t="inlineStr"/>
+      <c r="H10" s="10" t="n"/>
       <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
-      <c r="K10" s="8" t="inlineStr"/>
+      <c r="K10" s="10" t="n"/>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="n"/>
       <c r="O10" s="5" t="n"/>
-      <c r="P10" s="8" t="inlineStr"/>
+      <c r="P10" s="10" t="n"/>
       <c r="Q10" s="5" t="n"/>
       <c r="R10" s="5" t="n"/>
       <c r="S10" s="5" t="n"/>
       <c r="T10" s="5" t="n"/>
-      <c r="U10" s="8" t="inlineStr"/>
+      <c r="U10" s="9" t="n"/>
       <c r="V10" s="5" t="n"/>
-      <c r="W10" s="8" t="inlineStr"/>
+      <c r="W10" s="10" t="n"/>
       <c r="X10" s="5" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr"/>
+      <c r="A11" s="8">
+        <f>IF(K11="","",COUNTA(K9:K11))</f>
+        <v/>
+      </c>
       <c r="B11" s="5" t="n"/>
-      <c r="C11" s="8" t="inlineStr"/>
+      <c r="C11" s="9" t="n"/>
       <c r="D11" s="5" t="n"/>
-      <c r="E11" s="8" t="inlineStr"/>
+      <c r="E11" s="10" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
-      <c r="H11" s="8" t="inlineStr"/>
+      <c r="H11" s="10" t="n"/>
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
-      <c r="K11" s="8" t="inlineStr"/>
+      <c r="K11" s="10" t="n"/>
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="5" t="n"/>
       <c r="N11" s="5" t="n"/>
       <c r="O11" s="5" t="n"/>
-      <c r="P11" s="8" t="inlineStr"/>
+      <c r="P11" s="10" t="n"/>
       <c r="Q11" s="5" t="n"/>
       <c r="R11" s="5" t="n"/>
       <c r="S11" s="5" t="n"/>
       <c r="T11" s="5" t="n"/>
-      <c r="U11" s="8" t="inlineStr"/>
+      <c r="U11" s="9" t="n"/>
       <c r="V11" s="5" t="n"/>
-      <c r="W11" s="8" t="inlineStr"/>
+      <c r="W11" s="10" t="n"/>
       <c r="X11" s="5" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="8" t="inlineStr"/>
+      <c r="A12" s="8">
+        <f>IF(K12="","",COUNTA(K9:K12))</f>
+        <v/>
+      </c>
       <c r="B12" s="5" t="n"/>
-      <c r="C12" s="8" t="inlineStr"/>
+      <c r="C12" s="9" t="n"/>
       <c r="D12" s="5" t="n"/>
-      <c r="E12" s="8" t="inlineStr"/>
+      <c r="E12" s="10" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="5" t="n"/>
-      <c r="H12" s="8" t="inlineStr"/>
+      <c r="H12" s="10" t="n"/>
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
-      <c r="K12" s="8" t="inlineStr"/>
+      <c r="K12" s="10" t="n"/>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="5" t="n"/>
       <c r="N12" s="5" t="n"/>
       <c r="O12" s="5" t="n"/>
-      <c r="P12" s="8" t="inlineStr"/>
+      <c r="P12" s="10" t="n"/>
       <c r="Q12" s="5" t="n"/>
       <c r="R12" s="5" t="n"/>
       <c r="S12" s="5" t="n"/>
       <c r="T12" s="5" t="n"/>
-      <c r="U12" s="8" t="inlineStr"/>
+      <c r="U12" s="9" t="n"/>
       <c r="V12" s="5" t="n"/>
-      <c r="W12" s="8" t="inlineStr"/>
+      <c r="W12" s="10" t="n"/>
       <c r="X12" s="5" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="8" t="inlineStr"/>
+      <c r="A13" s="8">
+        <f>IF(K13="","",COUNTA(K9:K13))</f>
+        <v/>
+      </c>
       <c r="B13" s="5" t="n"/>
-      <c r="C13" s="8" t="inlineStr"/>
+      <c r="C13" s="9" t="n"/>
       <c r="D13" s="5" t="n"/>
-      <c r="E13" s="8" t="inlineStr"/>
+      <c r="E13" s="10" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
-      <c r="H13" s="8" t="inlineStr"/>
+      <c r="H13" s="10" t="n"/>
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
-      <c r="K13" s="8" t="inlineStr"/>
+      <c r="K13" s="10" t="n"/>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="5" t="n"/>
       <c r="N13" s="5" t="n"/>
       <c r="O13" s="5" t="n"/>
-      <c r="P13" s="8" t="inlineStr"/>
+      <c r="P13" s="10" t="n"/>
       <c r="Q13" s="5" t="n"/>
       <c r="R13" s="5" t="n"/>
       <c r="S13" s="5" t="n"/>
       <c r="T13" s="5" t="n"/>
-      <c r="U13" s="8" t="inlineStr"/>
+      <c r="U13" s="9" t="n"/>
       <c r="V13" s="5" t="n"/>
-      <c r="W13" s="8" t="inlineStr"/>
+      <c r="W13" s="10" t="n"/>
       <c r="X13" s="5" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8" t="inlineStr"/>
+      <c r="A14" s="8">
+        <f>IF(K14="","",COUNTA(K9:K14))</f>
+        <v/>
+      </c>
       <c r="B14" s="5" t="n"/>
-      <c r="C14" s="8" t="inlineStr"/>
+      <c r="C14" s="9" t="n"/>
       <c r="D14" s="5" t="n"/>
-      <c r="E14" s="8" t="inlineStr"/>
+      <c r="E14" s="10" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
-      <c r="H14" s="8" t="inlineStr"/>
+      <c r="H14" s="10" t="n"/>
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
-      <c r="K14" s="8" t="inlineStr"/>
+      <c r="K14" s="10" t="n"/>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="5" t="n"/>
       <c r="N14" s="5" t="n"/>
       <c r="O14" s="5" t="n"/>
-      <c r="P14" s="8" t="inlineStr"/>
+      <c r="P14" s="10" t="n"/>
       <c r="Q14" s="5" t="n"/>
       <c r="R14" s="5" t="n"/>
       <c r="S14" s="5" t="n"/>
       <c r="T14" s="5" t="n"/>
-      <c r="U14" s="8" t="inlineStr"/>
+      <c r="U14" s="9" t="n"/>
       <c r="V14" s="5" t="n"/>
-      <c r="W14" s="8" t="inlineStr"/>
+      <c r="W14" s="10" t="n"/>
       <c r="X14" s="5" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr"/>
+      <c r="A15" s="8">
+        <f>IF(K15="","",COUNTA(K9:K15))</f>
+        <v/>
+      </c>
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="8" t="inlineStr"/>
+      <c r="C15" s="9" t="n"/>
       <c r="D15" s="5" t="n"/>
-      <c r="E15" s="8" t="inlineStr"/>
+      <c r="E15" s="10" t="n"/>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="5" t="n"/>
-      <c r="H15" s="8" t="inlineStr"/>
+      <c r="H15" s="10" t="n"/>
       <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
-      <c r="K15" s="8" t="inlineStr"/>
+      <c r="K15" s="10" t="n"/>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="5" t="n"/>
       <c r="N15" s="5" t="n"/>
       <c r="O15" s="5" t="n"/>
-      <c r="P15" s="8" t="inlineStr"/>
+      <c r="P15" s="10" t="n"/>
       <c r="Q15" s="5" t="n"/>
       <c r="R15" s="5" t="n"/>
       <c r="S15" s="5" t="n"/>
       <c r="T15" s="5" t="n"/>
-      <c r="U15" s="8" t="inlineStr"/>
+      <c r="U15" s="9" t="n"/>
       <c r="V15" s="5" t="n"/>
-      <c r="W15" s="8" t="inlineStr"/>
+      <c r="W15" s="10" t="n"/>
       <c r="X15" s="5" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="8" t="inlineStr"/>
+      <c r="A16" s="8">
+        <f>IF(K16="","",COUNTA(K9:K16))</f>
+        <v/>
+      </c>
       <c r="B16" s="5" t="n"/>
-      <c r="C16" s="8" t="inlineStr"/>
+      <c r="C16" s="9" t="n"/>
       <c r="D16" s="5" t="n"/>
-      <c r="E16" s="8" t="inlineStr"/>
+      <c r="E16" s="10" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
-      <c r="H16" s="8" t="inlineStr"/>
+      <c r="H16" s="10" t="n"/>
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
-      <c r="K16" s="8" t="inlineStr"/>
+      <c r="K16" s="10" t="n"/>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="5" t="n"/>
       <c r="N16" s="5" t="n"/>
       <c r="O16" s="5" t="n"/>
-      <c r="P16" s="8" t="inlineStr"/>
+      <c r="P16" s="10" t="n"/>
       <c r="Q16" s="5" t="n"/>
       <c r="R16" s="5" t="n"/>
       <c r="S16" s="5" t="n"/>
       <c r="T16" s="5" t="n"/>
-      <c r="U16" s="8" t="inlineStr"/>
+      <c r="U16" s="9" t="n"/>
       <c r="V16" s="5" t="n"/>
-      <c r="W16" s="8" t="inlineStr"/>
+      <c r="W16" s="10" t="n"/>
       <c r="X16" s="5" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="8" t="inlineStr"/>
+      <c r="A17" s="8">
+        <f>IF(K17="","",COUNTA(K9:K17))</f>
+        <v/>
+      </c>
       <c r="B17" s="5" t="n"/>
-      <c r="C17" s="8" t="inlineStr"/>
+      <c r="C17" s="9" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="8" t="inlineStr"/>
+      <c r="E17" s="10" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
-      <c r="H17" s="8" t="inlineStr"/>
+      <c r="H17" s="10" t="n"/>
       <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
-      <c r="K17" s="8" t="inlineStr"/>
+      <c r="K17" s="10" t="n"/>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="5" t="n"/>
       <c r="N17" s="5" t="n"/>
       <c r="O17" s="5" t="n"/>
-      <c r="P17" s="8" t="inlineStr"/>
+      <c r="P17" s="10" t="n"/>
       <c r="Q17" s="5" t="n"/>
       <c r="R17" s="5" t="n"/>
       <c r="S17" s="5" t="n"/>
       <c r="T17" s="5" t="n"/>
-      <c r="U17" s="8" t="inlineStr"/>
+      <c r="U17" s="9" t="n"/>
       <c r="V17" s="5" t="n"/>
-      <c r="W17" s="8" t="inlineStr"/>
+      <c r="W17" s="10" t="n"/>
       <c r="X17" s="5" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8" t="inlineStr"/>
+      <c r="A18" s="8">
+        <f>IF(K18="","",COUNTA(K9:K18))</f>
+        <v/>
+      </c>
       <c r="B18" s="5" t="n"/>
-      <c r="C18" s="8" t="inlineStr"/>
+      <c r="C18" s="9" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="8" t="inlineStr"/>
+      <c r="E18" s="10" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="8" t="inlineStr"/>
+      <c r="H18" s="10" t="n"/>
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
-      <c r="K18" s="8" t="inlineStr"/>
+      <c r="K18" s="10" t="n"/>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="5" t="n"/>
       <c r="N18" s="5" t="n"/>
       <c r="O18" s="5" t="n"/>
-      <c r="P18" s="8" t="inlineStr"/>
+      <c r="P18" s="10" t="n"/>
       <c r="Q18" s="5" t="n"/>
       <c r="R18" s="5" t="n"/>
       <c r="S18" s="5" t="n"/>
       <c r="T18" s="5" t="n"/>
-      <c r="U18" s="8" t="inlineStr"/>
+      <c r="U18" s="9" t="n"/>
       <c r="V18" s="5" t="n"/>
-      <c r="W18" s="8" t="inlineStr"/>
+      <c r="W18" s="10" t="n"/>
       <c r="X18" s="5" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr"/>
+      <c r="A19" s="8">
+        <f>IF(K19="","",COUNTA(K9:K19))</f>
+        <v/>
+      </c>
       <c r="B19" s="5" t="n"/>
-      <c r="C19" s="8" t="inlineStr"/>
+      <c r="C19" s="9" t="n"/>
       <c r="D19" s="5" t="n"/>
-      <c r="E19" s="8" t="inlineStr"/>
+      <c r="E19" s="10" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
-      <c r="H19" s="8" t="inlineStr"/>
+      <c r="H19" s="10" t="n"/>
       <c r="I19" s="5" t="n"/>
       <c r="J19" s="5" t="n"/>
-      <c r="K19" s="8" t="inlineStr"/>
+      <c r="K19" s="10" t="n"/>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="5" t="n"/>
       <c r="N19" s="5" t="n"/>
       <c r="O19" s="5" t="n"/>
-      <c r="P19" s="8" t="inlineStr"/>
+      <c r="P19" s="10" t="n"/>
       <c r="Q19" s="5" t="n"/>
       <c r="R19" s="5" t="n"/>
       <c r="S19" s="5" t="n"/>
       <c r="T19" s="5" t="n"/>
-      <c r="U19" s="8" t="inlineStr"/>
+      <c r="U19" s="9" t="n"/>
       <c r="V19" s="5" t="n"/>
-      <c r="W19" s="8" t="inlineStr"/>
+      <c r="W19" s="10" t="n"/>
       <c r="X19" s="5" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="inlineStr"/>
+      <c r="A20" s="8">
+        <f>IF(K20="","",COUNTA(K9:K20))</f>
+        <v/>
+      </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="8" t="inlineStr"/>
+      <c r="C20" s="9" t="n"/>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="8" t="inlineStr"/>
+      <c r="E20" s="10" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
-      <c r="H20" s="8" t="inlineStr"/>
+      <c r="H20" s="10" t="n"/>
       <c r="I20" s="5" t="n"/>
       <c r="J20" s="5" t="n"/>
-      <c r="K20" s="8" t="inlineStr"/>
+      <c r="K20" s="10" t="n"/>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="5" t="n"/>
       <c r="N20" s="5" t="n"/>
       <c r="O20" s="5" t="n"/>
-      <c r="P20" s="8" t="inlineStr"/>
+      <c r="P20" s="10" t="n"/>
       <c r="Q20" s="5" t="n"/>
       <c r="R20" s="5" t="n"/>
       <c r="S20" s="5" t="n"/>
       <c r="T20" s="5" t="n"/>
-      <c r="U20" s="8" t="inlineStr"/>
+      <c r="U20" s="9" t="n"/>
       <c r="V20" s="5" t="n"/>
-      <c r="W20" s="8" t="inlineStr"/>
+      <c r="W20" s="10" t="n"/>
       <c r="X20" s="5" t="n"/>
     </row>
     <row r="21" ht="6" customHeight="1"/>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>※ 접수 경로: 방문 / 전화 / 공문 / 국민신문고 등</t>
         </is>
@@ -993,46 +1074,57 @@
     <row r="23" ht="6" customHeight="1"/>
     <row r="24" ht="10" customHeight="1"/>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="K26" s="11" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="13" t="inlineStr"/>
+      <c r="K26" s="14" t="inlineStr">
         <is>
           <t>현장대리인</t>
         </is>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="Q26" s="15" t="n"/>
+      <c r="U26" s="16" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="K27" s="11" t="inlineStr">
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="13" t="inlineStr"/>
+      <c r="K27" s="14" t="inlineStr">
         <is>
           <t>대표자</t>
         </is>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="Q27" s="15" t="n"/>
+      <c r="U27" s="16" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="6" customHeight="1"/>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>발주기관이 정한 서식이 있으면 그 서식을 사용하세요. 이 줄과 1행은 인쇄 전에 지우셔도 됩니다.</t>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19.5" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="118">
+  <mergeCells count="123">
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C15:D15"/>
@@ -1052,18 +1144,21 @@
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="A31:X31"/>
     <mergeCell ref="K17:O17"/>
+    <mergeCell ref="Q26:T26"/>
     <mergeCell ref="P12:T12"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="U20:V20"/>
     <mergeCell ref="U14:V14"/>
     <mergeCell ref="K10:O10"/>
+    <mergeCell ref="K26:P26"/>
     <mergeCell ref="W14:X14"/>
     <mergeCell ref="K19:O19"/>
     <mergeCell ref="P14:T14"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E20:G20"/>
     <mergeCell ref="K16:O16"/>
+    <mergeCell ref="Q27:T27"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A25:X25"/>
     <mergeCell ref="C14:D14"/>
@@ -1086,6 +1181,7 @@
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="U8:V8"/>
     <mergeCell ref="W8:X8"/>
+    <mergeCell ref="A30:X30"/>
     <mergeCell ref="W17:X17"/>
     <mergeCell ref="W11:X11"/>
     <mergeCell ref="E8:G8"/>
@@ -1102,9 +1198,9 @@
     <mergeCell ref="P20:T20"/>
     <mergeCell ref="E9:G9"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="K26:R26"/>
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="W20:X20"/>
+    <mergeCell ref="K27:P27"/>
     <mergeCell ref="H13:J13"/>
     <mergeCell ref="P8:T8"/>
     <mergeCell ref="A12:B12"/>
@@ -1115,12 +1211,12 @@
     <mergeCell ref="W12:X12"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="P16:T16"/>
-    <mergeCell ref="K27:R27"/>
     <mergeCell ref="E12:G12"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="H10:J10"/>
     <mergeCell ref="P18:T18"/>
     <mergeCell ref="E14:G14"/>
+    <mergeCell ref="A27:J27"/>
     <mergeCell ref="H9:J9"/>
     <mergeCell ref="K13:O13"/>
     <mergeCell ref="W10:X10"/>
@@ -1128,6 +1224,7 @@
     <mergeCell ref="G6:X6"/>
     <mergeCell ref="P9:T9"/>
     <mergeCell ref="A16:B16"/>
+    <mergeCell ref="U26:X26"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="U17:V17"/>
@@ -1137,22 +1234,809 @@
     <mergeCell ref="H12:J12"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="A18:B18"/>
+    <mergeCell ref="U27:X27"/>
     <mergeCell ref="H14:J14"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="S26:X26"/>
     <mergeCell ref="P13:T13"/>
     <mergeCell ref="W9:X9"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="S27:X27"/>
     <mergeCell ref="P15:T15"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="M1:X1"/>
+    <mergeCell ref="A26:J26"/>
     <mergeCell ref="W13:X13"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <dataValidations count="2">
+    <dataValidation sqref="E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
+      <formula1>"방문,전화,공문,국민신문고,기타"</formula1>
+    </dataValidation>
+    <dataValidation sqref="W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
+      <formula1>"○"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:X30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.6" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>민 원 접 수 · 처 리 대 장</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공 사 명</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  작성 기간</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>2026년 9월</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="6" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>접수일</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>접수 경로</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>민원인</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>민원 내용</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>조치 내용</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>회신일</t>
+        </is>
+      </c>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="7" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="X8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="8">
+        <f>IF(K9="","",COUNTA(K9:K9))</f>
+        <v/>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="9" t="n">
+        <v>46268</v>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>전화</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>마을 주민</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>공사 차량 먼지</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>살수 하루 3회로 늘림</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="5" t="n"/>
+      <c r="U9" s="9" t="n">
+        <v>46268</v>
+      </c>
+      <c r="V9" s="5" t="n"/>
+      <c r="W9" s="10" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8">
+        <f>IF(K10="","",COUNTA(K9:K10))</f>
+        <v/>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="9" t="n">
+        <v>46282</v>
+      </c>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>방문</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>상가 주인</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>가게 앞 출입 불편</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="10" t="inlineStr">
+        <is>
+          <t>임시 통로 설치</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="n"/>
+      <c r="R10" s="5" t="n"/>
+      <c r="S10" s="5" t="n"/>
+      <c r="T10" s="5" t="n"/>
+      <c r="U10" s="9" t="n">
+        <v>46283</v>
+      </c>
+      <c r="V10" s="5" t="n"/>
+      <c r="W10" s="10" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8">
+        <f>IF(K11="","",COUNTA(K9:K11))</f>
+        <v/>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="5" t="n"/>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" s="5" t="n"/>
+      <c r="T11" s="5" t="n"/>
+      <c r="U11" s="9" t="n"/>
+      <c r="V11" s="5" t="n"/>
+      <c r="W11" s="10" t="n"/>
+      <c r="X11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8">
+        <f>IF(K12="","",COUNTA(K9:K12))</f>
+        <v/>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="5" t="n"/>
+      <c r="R12" s="5" t="n"/>
+      <c r="S12" s="5" t="n"/>
+      <c r="T12" s="5" t="n"/>
+      <c r="U12" s="9" t="n"/>
+      <c r="V12" s="5" t="n"/>
+      <c r="W12" s="10" t="n"/>
+      <c r="X12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="8">
+        <f>IF(K13="","",COUNTA(K9:K13))</f>
+        <v/>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="5" t="n"/>
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="5" t="n"/>
+      <c r="T13" s="5" t="n"/>
+      <c r="U13" s="9" t="n"/>
+      <c r="V13" s="5" t="n"/>
+      <c r="W13" s="10" t="n"/>
+      <c r="X13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8">
+        <f>IF(K14="","",COUNTA(K9:K14))</f>
+        <v/>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="5" t="n"/>
+      <c r="R14" s="5" t="n"/>
+      <c r="S14" s="5" t="n"/>
+      <c r="T14" s="5" t="n"/>
+      <c r="U14" s="9" t="n"/>
+      <c r="V14" s="5" t="n"/>
+      <c r="W14" s="10" t="n"/>
+      <c r="X14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8">
+        <f>IF(K15="","",COUNTA(K9:K15))</f>
+        <v/>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="10" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="10" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="10" t="n"/>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="5" t="n"/>
+      <c r="U15" s="9" t="n"/>
+      <c r="V15" s="5" t="n"/>
+      <c r="W15" s="10" t="n"/>
+      <c r="X15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8">
+        <f>IF(K16="","",COUNTA(K9:K16))</f>
+        <v/>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="10" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="10" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="10" t="n"/>
+      <c r="Q16" s="5" t="n"/>
+      <c r="R16" s="5" t="n"/>
+      <c r="S16" s="5" t="n"/>
+      <c r="T16" s="5" t="n"/>
+      <c r="U16" s="9" t="n"/>
+      <c r="V16" s="5" t="n"/>
+      <c r="W16" s="10" t="n"/>
+      <c r="X16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8">
+        <f>IF(K17="","",COUNTA(K9:K17))</f>
+        <v/>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="10" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="10" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="10" t="n"/>
+      <c r="Q17" s="5" t="n"/>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" s="5" t="n"/>
+      <c r="T17" s="5" t="n"/>
+      <c r="U17" s="9" t="n"/>
+      <c r="V17" s="5" t="n"/>
+      <c r="W17" s="10" t="n"/>
+      <c r="X17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8">
+        <f>IF(K18="","",COUNTA(K9:K18))</f>
+        <v/>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="10" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="5" t="n"/>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="5" t="n"/>
+      <c r="T18" s="5" t="n"/>
+      <c r="U18" s="9" t="n"/>
+      <c r="V18" s="5" t="n"/>
+      <c r="W18" s="10" t="n"/>
+      <c r="X18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8">
+        <f>IF(K19="","",COUNTA(K9:K19))</f>
+        <v/>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="5" t="n"/>
+      <c r="T19" s="5" t="n"/>
+      <c r="U19" s="9" t="n"/>
+      <c r="V19" s="5" t="n"/>
+      <c r="W19" s="10" t="n"/>
+      <c r="X19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8">
+        <f>IF(K20="","",COUNTA(K9:K20))</f>
+        <v/>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="10" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="10" t="n"/>
+      <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="5" t="n"/>
+      <c r="T20" s="5" t="n"/>
+      <c r="U20" s="9" t="n"/>
+      <c r="V20" s="5" t="n"/>
+      <c r="W20" s="10" t="n"/>
+      <c r="X20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="6" customHeight="1"/>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>※ 접수 경로: 방문 / 전화 / 공문 / 국민신문고 등</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="6" customHeight="1"/>
+    <row r="24" ht="10" customHeight="1"/>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="12" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="13" t="inlineStr"/>
+      <c r="K26" s="14" t="inlineStr">
+        <is>
+          <t>현장대리인</t>
+        </is>
+      </c>
+      <c r="Q26" s="15" t="inlineStr">
+        <is>
+          <t>김철수</t>
+        </is>
+      </c>
+      <c r="U26" s="16" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="13" t="inlineStr"/>
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>대표자</t>
+        </is>
+      </c>
+      <c r="Q27" s="15" t="inlineStr">
+        <is>
+          <t>홍길동</t>
+        </is>
+      </c>
+      <c r="U27" s="16" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="6" customHeight="1"/>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="122">
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="P10:T10"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="K17:O17"/>
+    <mergeCell ref="Q26:T26"/>
+    <mergeCell ref="P12:T12"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="U20:V20"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="K10:O10"/>
+    <mergeCell ref="K26:P26"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="K19:O19"/>
+    <mergeCell ref="P14:T14"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="K16:O16"/>
+    <mergeCell ref="Q27:T27"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A25:X25"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="K9:O9"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K20:O20"/>
+    <mergeCell ref="K11:O11"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="A22:X22"/>
+    <mergeCell ref="K12:O12"/>
+    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="P17:T17"/>
+    <mergeCell ref="K8:O8"/>
+    <mergeCell ref="K14:O14"/>
+    <mergeCell ref="U18:V18"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="W18:X18"/>
+    <mergeCell ref="P19:T19"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="W8:X8"/>
+    <mergeCell ref="A30:X30"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="U10:V10"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="U19:V19"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="K18:O18"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="P20:T20"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="W20:X20"/>
+    <mergeCell ref="K27:P27"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="P8:T8"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="P16:T16"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="P18:T18"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K13:O13"/>
+    <mergeCell ref="W10:X10"/>
+    <mergeCell ref="K15:O15"/>
+    <mergeCell ref="G6:X6"/>
+    <mergeCell ref="P9:T9"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="U26:X26"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="G5:X5"/>
+    <mergeCell ref="P11:T11"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="P13:T13"/>
+    <mergeCell ref="W9:X9"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="P15:T15"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="M1:X1"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="W13:X13"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
+      <formula1>"방문,전화,공문,국민신문고,기타"</formula1>
+    </dataValidation>
+    <dataValidation sqref="W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
+      <formula1>"○"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/minwon.xlsx
+++ b/web/public/forms/minwon.xlsx
@@ -578,7 +578,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="18" t="inlineStr">

--- a/web/public/forms/minwon.xlsx
+++ b/web/public/forms/minwon.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="민원 접수·처리대장" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'민원 접수·처리대장'!$A$1:$X$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -127,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -177,9 +175,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -716,10 +711,7 @@
       <c r="X8" s="5" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="8">
-        <f>IF(K9="","",COUNTA(K9:K9))</f>
-        <v/>
-      </c>
+      <c r="A9" s="8" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="5" t="n"/>
@@ -745,10 +737,7 @@
       <c r="X9" s="5" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8">
-        <f>IF(K10="","",COUNTA(K9:K10))</f>
-        <v/>
-      </c>
+      <c r="A10" s="8" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="9" t="n"/>
       <c r="D10" s="5" t="n"/>
@@ -774,10 +763,7 @@
       <c r="X10" s="5" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8">
-        <f>IF(K11="","",COUNTA(K9:K11))</f>
-        <v/>
-      </c>
+      <c r="A11" s="8" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="9" t="n"/>
       <c r="D11" s="5" t="n"/>
@@ -803,10 +789,7 @@
       <c r="X11" s="5" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="8">
-        <f>IF(K12="","",COUNTA(K9:K12))</f>
-        <v/>
-      </c>
+      <c r="A12" s="8" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="9" t="n"/>
       <c r="D12" s="5" t="n"/>
@@ -832,10 +815,7 @@
       <c r="X12" s="5" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="8">
-        <f>IF(K13="","",COUNTA(K9:K13))</f>
-        <v/>
-      </c>
+      <c r="A13" s="8" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="5" t="n"/>
@@ -861,10 +841,7 @@
       <c r="X13" s="5" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8">
-        <f>IF(K14="","",COUNTA(K9:K14))</f>
-        <v/>
-      </c>
+      <c r="A14" s="8" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="9" t="n"/>
       <c r="D14" s="5" t="n"/>
@@ -890,10 +867,7 @@
       <c r="X14" s="5" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8">
-        <f>IF(K15="","",COUNTA(K9:K15))</f>
-        <v/>
-      </c>
+      <c r="A15" s="8" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="9" t="n"/>
       <c r="D15" s="5" t="n"/>
@@ -919,10 +893,7 @@
       <c r="X15" s="5" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="8">
-        <f>IF(K16="","",COUNTA(K9:K16))</f>
-        <v/>
-      </c>
+      <c r="A16" s="8" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="9" t="n"/>
       <c r="D16" s="5" t="n"/>
@@ -948,10 +919,7 @@
       <c r="X16" s="5" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="8">
-        <f>IF(K17="","",COUNTA(K9:K17))</f>
-        <v/>
-      </c>
+      <c r="A17" s="8" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="9" t="n"/>
       <c r="D17" s="5" t="n"/>
@@ -977,10 +945,7 @@
       <c r="X17" s="5" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8">
-        <f>IF(K18="","",COUNTA(K9:K18))</f>
-        <v/>
-      </c>
+      <c r="A18" s="8" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="9" t="n"/>
       <c r="D18" s="5" t="n"/>
@@ -1006,10 +971,7 @@
       <c r="X18" s="5" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8">
-        <f>IF(K19="","",COUNTA(K9:K19))</f>
-        <v/>
-      </c>
+      <c r="A19" s="8" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="9" t="n"/>
       <c r="D19" s="5" t="n"/>
@@ -1035,10 +997,7 @@
       <c r="X19" s="5" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8">
-        <f>IF(K20="","",COUNTA(K9:K20))</f>
-        <v/>
-      </c>
+      <c r="A20" s="8" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="5" t="n"/>
@@ -1109,6 +1068,7 @@
       </c>
     </row>
     <row r="28" ht="6" customHeight="1"/>
+    <row r="29"/>
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
@@ -1261,782 +1221,4 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>민 원 접 수 · 처 리 대 장</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공 사 명</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  작성 기간</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>2026년 9월</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="6" customHeight="1"/>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>접수일</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>접수 경로</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>민원인</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>민원 내용</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>조치 내용</t>
-        </is>
-      </c>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>회신일</t>
-        </is>
-      </c>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="7" t="inlineStr">
-        <is>
-          <t>종결</t>
-        </is>
-      </c>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="8">
-        <f>IF(K9="","",COUNTA(K9:K9))</f>
-        <v/>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="9" t="n">
-        <v>46268</v>
-      </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>전화</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>마을 주민</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>공사 차량 먼지</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="10" t="inlineStr">
-        <is>
-          <t>살수 하루 3회로 늘림</t>
-        </is>
-      </c>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="9" t="n">
-        <v>46268</v>
-      </c>
-      <c r="V9" s="5" t="n"/>
-      <c r="W9" s="10" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="X9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8">
-        <f>IF(K10="","",COUNTA(K9:K10))</f>
-        <v/>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="9" t="n">
-        <v>46282</v>
-      </c>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>방문</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>상가 주인</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t>가게 앞 출입 불편</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="10" t="inlineStr">
-        <is>
-          <t>임시 통로 설치</t>
-        </is>
-      </c>
-      <c r="Q10" s="5" t="n"/>
-      <c r="R10" s="5" t="n"/>
-      <c r="S10" s="5" t="n"/>
-      <c r="T10" s="5" t="n"/>
-      <c r="U10" s="9" t="n">
-        <v>46283</v>
-      </c>
-      <c r="V10" s="5" t="n"/>
-      <c r="W10" s="10" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="X10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8">
-        <f>IF(K11="","",COUNTA(K9:K11))</f>
-        <v/>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="10" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="10" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-      <c r="P11" s="10" t="n"/>
-      <c r="Q11" s="5" t="n"/>
-      <c r="R11" s="5" t="n"/>
-      <c r="S11" s="5" t="n"/>
-      <c r="T11" s="5" t="n"/>
-      <c r="U11" s="9" t="n"/>
-      <c r="V11" s="5" t="n"/>
-      <c r="W11" s="10" t="n"/>
-      <c r="X11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="8">
-        <f>IF(K12="","",COUNTA(K9:K12))</f>
-        <v/>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="10" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="10" t="n"/>
-      <c r="Q12" s="5" t="n"/>
-      <c r="R12" s="5" t="n"/>
-      <c r="S12" s="5" t="n"/>
-      <c r="T12" s="5" t="n"/>
-      <c r="U12" s="9" t="n"/>
-      <c r="V12" s="5" t="n"/>
-      <c r="W12" s="10" t="n"/>
-      <c r="X12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="8">
-        <f>IF(K13="","",COUNTA(K9:K13))</f>
-        <v/>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="10" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="10" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="10" t="n"/>
-      <c r="Q13" s="5" t="n"/>
-      <c r="R13" s="5" t="n"/>
-      <c r="S13" s="5" t="n"/>
-      <c r="T13" s="5" t="n"/>
-      <c r="U13" s="9" t="n"/>
-      <c r="V13" s="5" t="n"/>
-      <c r="W13" s="10" t="n"/>
-      <c r="X13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8">
-        <f>IF(K14="","",COUNTA(K9:K14))</f>
-        <v/>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="10" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="10" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="10" t="n"/>
-      <c r="Q14" s="5" t="n"/>
-      <c r="R14" s="5" t="n"/>
-      <c r="S14" s="5" t="n"/>
-      <c r="T14" s="5" t="n"/>
-      <c r="U14" s="9" t="n"/>
-      <c r="V14" s="5" t="n"/>
-      <c r="W14" s="10" t="n"/>
-      <c r="X14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8">
-        <f>IF(K15="","",COUNTA(K9:K15))</f>
-        <v/>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="10" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="10" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="10" t="n"/>
-      <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" s="5" t="n"/>
-      <c r="T15" s="5" t="n"/>
-      <c r="U15" s="9" t="n"/>
-      <c r="V15" s="5" t="n"/>
-      <c r="W15" s="10" t="n"/>
-      <c r="X15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="8">
-        <f>IF(K16="","",COUNTA(K9:K16))</f>
-        <v/>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="10" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="10" t="n"/>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-      <c r="P16" s="10" t="n"/>
-      <c r="Q16" s="5" t="n"/>
-      <c r="R16" s="5" t="n"/>
-      <c r="S16" s="5" t="n"/>
-      <c r="T16" s="5" t="n"/>
-      <c r="U16" s="9" t="n"/>
-      <c r="V16" s="5" t="n"/>
-      <c r="W16" s="10" t="n"/>
-      <c r="X16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="8">
-        <f>IF(K17="","",COUNTA(K9:K17))</f>
-        <v/>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="10" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="10" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="10" t="n"/>
-      <c r="Q17" s="5" t="n"/>
-      <c r="R17" s="5" t="n"/>
-      <c r="S17" s="5" t="n"/>
-      <c r="T17" s="5" t="n"/>
-      <c r="U17" s="9" t="n"/>
-      <c r="V17" s="5" t="n"/>
-      <c r="W17" s="10" t="n"/>
-      <c r="X17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8">
-        <f>IF(K18="","",COUNTA(K9:K18))</f>
-        <v/>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="10" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="10" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="10" t="n"/>
-      <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="5" t="n"/>
-      <c r="T18" s="5" t="n"/>
-      <c r="U18" s="9" t="n"/>
-      <c r="V18" s="5" t="n"/>
-      <c r="W18" s="10" t="n"/>
-      <c r="X18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8">
-        <f>IF(K19="","",COUNTA(K9:K19))</f>
-        <v/>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="10" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="10" t="n"/>
-      <c r="Q19" s="5" t="n"/>
-      <c r="R19" s="5" t="n"/>
-      <c r="S19" s="5" t="n"/>
-      <c r="T19" s="5" t="n"/>
-      <c r="U19" s="9" t="n"/>
-      <c r="V19" s="5" t="n"/>
-      <c r="W19" s="10" t="n"/>
-      <c r="X19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8">
-        <f>IF(K20="","",COUNTA(K9:K20))</f>
-        <v/>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="10" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="10" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="10" t="n"/>
-      <c r="Q20" s="5" t="n"/>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="5" t="n"/>
-      <c r="T20" s="5" t="n"/>
-      <c r="U20" s="9" t="n"/>
-      <c r="V20" s="5" t="n"/>
-      <c r="W20" s="10" t="n"/>
-      <c r="X20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="6" customHeight="1"/>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>※ 접수 경로: 방문 / 전화 / 공문 / 국민신문고 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="6" customHeight="1"/>
-    <row r="24" ht="10" customHeight="1"/>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="12" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="13" t="inlineStr"/>
-      <c r="K26" s="14" t="inlineStr">
-        <is>
-          <t>현장대리인</t>
-        </is>
-      </c>
-      <c r="Q26" s="15" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="U26" s="16" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="13" t="inlineStr"/>
-      <c r="K27" s="14" t="inlineStr">
-        <is>
-          <t>대표자</t>
-        </is>
-      </c>
-      <c r="Q27" s="15" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="U27" s="16" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="6" customHeight="1"/>
-    <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="122">
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="W15:X15"/>
-    <mergeCell ref="P10:T10"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="K17:O17"/>
-    <mergeCell ref="Q26:T26"/>
-    <mergeCell ref="P12:T12"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="U20:V20"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="K10:O10"/>
-    <mergeCell ref="K26:P26"/>
-    <mergeCell ref="W14:X14"/>
-    <mergeCell ref="K19:O19"/>
-    <mergeCell ref="P14:T14"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="K16:O16"/>
-    <mergeCell ref="Q27:T27"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A25:X25"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="K9:O9"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="K20:O20"/>
-    <mergeCell ref="K11:O11"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="A22:X22"/>
-    <mergeCell ref="K12:O12"/>
-    <mergeCell ref="W16:X16"/>
-    <mergeCell ref="P17:T17"/>
-    <mergeCell ref="K8:O8"/>
-    <mergeCell ref="K14:O14"/>
-    <mergeCell ref="U18:V18"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="W18:X18"/>
-    <mergeCell ref="P19:T19"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="W8:X8"/>
-    <mergeCell ref="A30:X30"/>
-    <mergeCell ref="W17:X17"/>
-    <mergeCell ref="W11:X11"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="U10:V10"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="U19:V19"/>
-    <mergeCell ref="W19:X19"/>
-    <mergeCell ref="K18:O18"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="U9:V9"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="P20:T20"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="W20:X20"/>
-    <mergeCell ref="K27:P27"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="P8:T8"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="U12:V12"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="W12:X12"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="P16:T16"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="P18:T18"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K13:O13"/>
-    <mergeCell ref="W10:X10"/>
-    <mergeCell ref="K15:O15"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="P9:T9"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="U26:X26"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="P11:T11"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="U27:X27"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="P13:T13"/>
-    <mergeCell ref="W9:X9"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="P15:T15"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="W13:X13"/>
-  </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"방문,전화,공문,국민신문고,기타"</formula1>
-    </dataValidation>
-    <dataValidation sqref="W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"○"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/minwon.xlsx
+++ b/web/public/forms/minwon.xlsx
@@ -573,7 +573,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
